--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_support_assessment.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_support_assessment.xlsx
@@ -450,9 +450,9 @@
     <col width="25" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
     <col width="29" customWidth="1" min="22" max="22"/>
-    <col width="24" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="23" max="23"/>
     <col width="17" customWidth="1" min="24" max="24"/>
     <col width="45" customWidth="1" min="25" max="25"/>
     <col width="45" customWidth="1" min="26" max="26"/>
@@ -675,22 +675,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5951</v>
+        <v>9494</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="H2" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="I2" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -733,17 +733,17 @@
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>6.979122137092219</v>
+        <v>2.34344395669909</v>
       </c>
       <c r="W2" t="n">
-        <v>0.143284496295782</v>
+        <v>0.4267223874252885</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>7573a9ad1114f6741c09d6ac5d81c7514a81471ca3d0a0e1119a57b917521dff</t>
+          <t>abdea51b860497fc1b65b8107202a33c5eb4b613dfb71dc4bc9253e7c41cf23e</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10826</v>
+        <v>6877</v>
       </c>
       <c r="G3" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H3" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I3" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -853,17 +853,17 @@
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>2.147483726913584</v>
+        <v>1.658152502991723</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4656612701960841</v>
+        <v>0.6030808373751808</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>240e42fb4288efafd579caefad5823f173a0ba8b39a76df61ecc2bd97e38820c</t>
+          <t>9b64efc6f0dd32bc67a239eadf99ce765fd105a1787ad70df698a2d9c7634b96</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4017</v>
+        <v>3745</v>
       </c>
       <c r="G4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -973,17 +973,17 @@
         <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>7.100296517715128</v>
+        <v>10.91503976643994</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1408391885472692</v>
+        <v>0.09161670698394173</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>799fd122bc98ce27426a0b3cc5f164169f9a6d7a5a11d692194bb8f1fc46354f</t>
+          <t>a4aaba002ac82a08dda34dba7ad4e4f9dc9719448181db8832de39d05ea5ee22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1035,16 +1035,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4903</v>
+        <v>5581</v>
       </c>
       <c r="G5" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H5" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I5" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -1093,17 +1093,17 @@
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>43.52860443396614</v>
+        <v>60.08553334435669</v>
       </c>
       <c r="W5" t="n">
-        <v>0.022973399055718</v>
+        <v>0.01664294122628307</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>8e83a9651e10e4dadb52de9a7a4ca35e4ba16def58f928397989e61923e7f4b1</t>
+          <t>abd1e4cde2783685a74e7c221178b6478293e37ed48758c416f3cbc504c19296</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10826</v>
+        <v>9494</v>
       </c>
       <c r="G6" t="n">
         <v>76</v>
@@ -1213,17 +1213,17 @@
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>2.147483726913584</v>
+        <v>2.34344395669909</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4656612701960841</v>
+        <v>0.4267223874252885</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>7ee0ba6c6921dcd84a704d4a87f3fab2c63c84261438c5cdd018c90cd399087b</t>
+          <t>85bca70fde6b2e1d654d87d2ae97b54812b3bb28d37339d208a812bfd6f29c2d</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1275,16 +1275,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4505</v>
+        <v>6877</v>
       </c>
       <c r="G7" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="H7" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="I7" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -1333,17 +1333,17 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>84.84831439740255</v>
+        <v>1.658152502991723</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01178573796193897</v>
+        <v>0.6030808373751808</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>b8bcb9601c0a95059be1c7d933bfe3464cf10eee2a0785f46bbc7179410938f6</t>
+          <t>4ef037901c0e763323e341ffb6e9f58d2450465d7f120798609ed300cc6e38cd</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1395,16 +1395,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4546</v>
+        <v>3745</v>
       </c>
       <c r="G8" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H8" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="I8" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -1453,17 +1453,17 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>12.01217871242618</v>
+        <v>10.91503976643994</v>
       </c>
       <c r="W8" t="n">
-        <v>0.083248844688394</v>
+        <v>0.09161670698394173</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>c5c4c851c54dd01888f6c40b3881608eac14c12eb99c8e953a47656f6a4ce786</t>
+          <t>68781020732c583eee92cf61f32f95b45db7eeefafc5a0e63955bb1d1acaa43f</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1515,22 +1515,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5820</v>
+        <v>5581</v>
       </c>
       <c r="G9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1573,17 +1573,17 @@
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>6.95147536263732</v>
+        <v>60.08553334435669</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1438543543396247</v>
+        <v>0.01664294122628307</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>250f28f08573e2f106730a8fd0a96623395dbe5057ae6663f64ea033e0926567</t>
+          <t>5579197096f667e86500c1b654693513af672f096cd8755535d88ebf2751d9cf</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1635,19 +1635,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7135</v>
+        <v>9494</v>
       </c>
       <c r="G10" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H10" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="I10" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -1693,17 +1693,17 @@
         <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>36.27375006447572</v>
+        <v>2.34344395669909</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02756814495944103</v>
+        <v>0.4267223874252885</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>dfdaffe16a096cd2bb2513755334de4a842d471d04f24eb4f9b3a9be4f823b20</t>
+          <t>1c31a0e46fc9ded7f2002a45fefb02020badecd80cdad6328c97f65f4488febe</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1755,22 +1755,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7732</v>
+        <v>6877</v>
       </c>
       <c r="G11" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H11" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I11" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1813,17 +1813,17 @@
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>14.40534233320403</v>
+        <v>1.658152502991723</v>
       </c>
       <c r="W11" t="n">
-        <v>0.06941869043230024</v>
+        <v>0.6030808373751808</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>69c1b96792da9ec9c227476ad1d08b142a5b12aa481b373158756991cef6939b</t>
+          <t>0521c690ccc42e977d420c4fa4f20d1fb750179d6cf31452df4d7b85019e74a5</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1875,19 +1875,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6278</v>
+        <v>3745</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="H12" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="I12" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -1933,17 +1933,17 @@
         <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>3.293391817751925</v>
+        <v>10.91503976643994</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3036383325572849</v>
+        <v>0.09161670698394173</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1f3723222073f81be868ecb37dd158441c6f2d241b7e09b0f594af45799216c3</t>
+          <t>7f0a8af032795d53422a456427a61b6fc6b4e8c04a784ffa163e4a81c16f940d</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4552</v>
+        <v>5581</v>
       </c>
       <c r="G13" t="n">
         <v>46</v>
@@ -2053,17 +2053,17 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>9.038537301647649</v>
+        <v>60.08553334435669</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1106373704756087</v>
+        <v>0.01664294122628307</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>3e27dfe6d87cf4b1ad45c470c3d7c4df3cb0901ec3d645d9f65c2820f77d0f9f</t>
+          <t>192e2e3acc2cb7f14771418553f29f5470c80d7e76298c386ccf116cefa9b878</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3696</v>
+        <v>9494</v>
       </c>
       <c r="G14" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="H14" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>2</v>
@@ -2167,23 +2167,23 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>1</v>
       </c>
       <c r="V14" t="n">
-        <v>635.5760658556907</v>
+        <v>4548632244.376826</v>
       </c>
       <c r="W14" t="n">
-        <v>0.001573375798306182</v>
+        <v>2.198463068181065e-10</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0ec1db178dca7b91d2fb27cc03d78fb09e7202301b8dbde3b51c9c71d0bc4d64</t>
+          <t>a1c7b40a3132bae1fe439735761785a3d781c4984759cdce66634cc2cedc86c6</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10826</v>
+        <v>6877</v>
       </c>
       <c r="G15" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H15" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I15" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J15" t="n">
         <v>3</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -2278,32 +2278,32 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>full_shrinkage</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>oas</t>
         </is>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0.0004298512162779192</v>
       </c>
       <c r="V15" t="n">
-        <v>8348874021.949664</v>
+        <v>586.3983258039873</v>
       </c>
       <c r="W15" t="n">
-        <v>1.197766306415623e-10</v>
+        <v>0.001705325469046873</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>97e90e74ceeda8242d55446f135a9be2602f11e3da8ac917f06af8e118169070</t>
+          <t>7b99b164f3ef6b07c79aeb92ad07985807e687e4fed0b5134a233f3d49a75475</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2355,19 +2355,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4129</v>
+        <v>3745</v>
       </c>
       <c r="G16" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="H16" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="I16" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
@@ -2413,17 +2413,17 @@
         <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>563532300.4780883</v>
+        <v>646.3054840670832</v>
       </c>
       <c r="W16" t="n">
-        <v>1.774521175009174e-09</v>
+        <v>0.001547255941118094</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>7c0be58bdb2f4f246db9eb2e4c7a52dfa250fc6c114d23e3d42d79606266cb3c</t>
+          <t>1b2cb7dcdfb2637934e1963c48f936bb597aa6ffd1260145c9aaae5556c97d22</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2475,22 +2475,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>7046</v>
+        <v>5581</v>
       </c>
       <c r="G17" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="H17" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I17" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="J17" t="n">
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2527,23 +2527,23 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>475.4205510173314</v>
+        <v>171822144.318474</v>
       </c>
       <c r="W17" t="n">
-        <v>0.00210340086868383</v>
+        <v>5.819971598925518e-09</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>b6133348da302abd546520db2a5ed7be59b770efb041422b51e3240ab59cf8db</t>
+          <t>6e29ae2c103d43c43a5d3c04fdf0922c82db479d85bb75779e1162912a599314</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2595,19 +2595,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2963</v>
+        <v>9494</v>
       </c>
       <c r="G18" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="H18" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -2647,23 +2647,23 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>224.4920372005897</v>
+        <v>4548632244.376826</v>
       </c>
       <c r="W18" t="n">
-        <v>0.004454500981281901</v>
+        <v>2.198463068181065e-10</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>dd641d5350d63df90976af7e45a2ca8c01b6e802269e7e667e9cccef63d47cd8</t>
+          <t>6011c4062b63c4fe6b193578d871299751d206923a96a85cd1da9298e753d52f</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2715,16 +2715,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4584</v>
+        <v>6877</v>
       </c>
       <c r="G19" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="H19" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="I19" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="J19" t="n">
         <v>3</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2758,32 +2758,32 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>full_shrinkage</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>oas</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0.0004298512162779192</v>
       </c>
       <c r="V19" t="n">
-        <v>230977645.401689</v>
+        <v>586.3983258039873</v>
       </c>
       <c r="W19" t="n">
-        <v>4.329423300947233e-09</v>
+        <v>0.001705325469046873</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>eed3e866b9b5c90f6ffc6cb6bf6d3416671e988c6ab1275d0956859897d25aad</t>
+          <t>124cfb18585941ef92e2001815553f7a971580a657f673d1a5582bc7a61eb0ac</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2835,22 +2835,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7332</v>
+        <v>3745</v>
       </c>
       <c r="G20" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="H20" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="I20" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2887,23 +2887,23 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>1</v>
       </c>
       <c r="V20" t="n">
-        <v>463.8799227317832</v>
+        <v>646.3054840670832</v>
       </c>
       <c r="W20" t="n">
-        <v>0.002155730289233067</v>
+        <v>0.001547255941118094</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>d253da117d6ab6f5ea856dce095b24a0d03606936c1039f9d1d73d688005433c</t>
+          <t>163795178cb2ff51ce61ddc80b82e54e3402a0b2bb8e99fe2ade3f23df774ac2</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10818</v>
+        <v>5581</v>
       </c>
       <c r="G21" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="H21" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="I21" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="J21" t="n">
         <v>3</v>
@@ -3007,23 +3007,23 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>8349431833.252301</v>
+        <v>171822144.318474</v>
       </c>
       <c r="W21" t="n">
-        <v>1.197686285691222e-10</v>
+        <v>5.819971598925518e-09</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>662dd912877f5a0cee76422f0d1cfebc413b6c90082b5d852de19347f2e2eacc</t>
+          <t>e9690c753833b658d92c1d1fa7b906dc3597d30c2dfb2dfa650b94eb349ca09a</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3075,16 +3075,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>9916</v>
+        <v>9494</v>
       </c>
       <c r="G22" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H22" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I22" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J22" t="n">
         <v>3</v>
@@ -3133,17 +3133,17 @@
         <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>12562561805.13429</v>
+        <v>4548632244.376826</v>
       </c>
       <c r="W22" t="n">
-        <v>7.960159842487718e-11</v>
+        <v>2.198463068181065e-10</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>4b0ebc86d117d7902bed3f53431d77a9c043ad5977e02262474e2d1737528aa7</t>
+          <t>3e2ccd21062857aeb76fc468daf0e779f5b839da3fca7a760c444d714687b567</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3195,26 +3195,26 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1003</v>
+        <v>6877</v>
       </c>
       <c r="G23" t="n">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="H23" t="n">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="I23" t="n">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>2</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -3238,32 +3238,32 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>full_shrinkage</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>oas</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0.0004298512162779192</v>
       </c>
       <c r="V23" t="n">
-        <v>121734762873.2452</v>
+        <v>586.3983258039873</v>
       </c>
       <c r="W23" t="n">
-        <v>8.214580423845224e-12</v>
+        <v>0.001705325469046873</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>694c323e43f23587e51e7f9be99d42ae0391286303eae1510325a57e4d8970f0</t>
+          <t>cc30ef322555343c07e03ebbae65fa1aff449c7cf32dc6429960014478228e00</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3315,16 +3315,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5239</v>
+        <v>3745</v>
       </c>
       <c r="G24" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="H24" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="I24" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
         <v>2</v>
@@ -3367,23 +3367,23 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
       <c r="V24" t="n">
-        <v>2006016088.371842</v>
+        <v>646.3054840670832</v>
       </c>
       <c r="W24" t="n">
-        <v>4.985004885038772e-10</v>
+        <v>0.001547255941118094</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>f565d1dfc4900a9b4f69e50ab94259bf3ef98e7a98c6cf95403a931d5c12a590</t>
+          <t>1969ab355c6fb71ecae7af47809ec461e801d4aaf7c0cd9e1f4042d6fe01612c</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3435,26 +3435,26 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>9539</v>
+        <v>5581</v>
       </c>
       <c r="G25" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="H25" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="I25" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
         <v>2</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -3478,32 +3478,32 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>full_shrinkage</t>
+          <t>diagonal_robust_z</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>oas</t>
+          <t>diagonal_robust_z</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0003864903680573411</v>
+        <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>216.1152454812279</v>
+        <v>171822144.318474</v>
       </c>
       <c r="W25" t="n">
-        <v>0.004627160836216201</v>
+        <v>5.819971598925518e-09</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>e7ffd2923c4072c5614bcb45cb6b7641301fab200881895e1ba288fda90cf60d</t>
+          <t>40d2dc4419104e2565f907677701af5d7520b3c1a66785887c2e8af250182fa9</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10826</v>
+        <v>9494</v>
       </c>
       <c r="G26" t="n">
         <v>76</v>
@@ -3613,17 +3613,17 @@
         <v>1</v>
       </c>
       <c r="V26" t="n">
-        <v>8348874021.949664</v>
+        <v>4548632244.376826</v>
       </c>
       <c r="W26" t="n">
-        <v>1.197766306415623e-10</v>
+        <v>2.198463068181065e-10</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>e166958c74da300f2c97d63244695bcac52eea874f58e00d665189a216a3df5e</t>
+          <t>dd39d1c8e6ced0f9e58e8aa923803d356b6e61f3ca84af6e50d26e883ca3ec9b</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3675,16 +3675,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4020</v>
+        <v>6877</v>
       </c>
       <c r="G27" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="H27" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="I27" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="J27" t="n">
         <v>3</v>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -3718,32 +3718,32 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>full_shrinkage</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>oas</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0.0004298512162779192</v>
       </c>
       <c r="V27" t="n">
-        <v>183696817.3404491</v>
+        <v>586.3983258039873</v>
       </c>
       <c r="W27" t="n">
-        <v>5.443752452970806e-09</v>
+        <v>0.001705325469046873</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>31e6b6e9e4d668a457d7b2e8c92e91259ee1f49497baf640c9ed97524fd77cdf</t>
+          <t>13258aa831b746f55061aa4eb3753a9fce1281b5758506b8ddef633b6548a604</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3676</v>
+        <v>3745</v>
       </c>
       <c r="G28" t="n">
         <v>29</v>
@@ -3853,17 +3853,17 @@
         <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>533.8771075495655</v>
+        <v>646.3054840670832</v>
       </c>
       <c r="W28" t="n">
-        <v>0.001873090240916837</v>
+        <v>0.001547255941118094</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>91a404a3ace45b1f2683cfdbd15d07a6996943f0d48383eccac2dfff5d9f9ea6</t>
+          <t>ffd319fa76b84e7f36ef4ee99cb269065801e7fa2d07296cb1e91ec11da558f1</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3915,22 +3915,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7175</v>
+        <v>5581</v>
       </c>
       <c r="G29" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H29" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I29" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J29" t="n">
         <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3967,23 +3967,23 @@
         </is>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="V29" t="n">
-        <v>480.3296353762532</v>
+        <v>171822144.318474</v>
       </c>
       <c r="W29" t="n">
-        <v>0.002081903606086427</v>
+        <v>5.819971598925518e-09</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>10b37d0fd36bd9404a1227df39fb19649281bdc6dde9452094912f16ba82e0fc</t>
+          <t>d92b1d085d188c63ef369f7fa10d8e8c9dadf3aedd9cba2ec974b87be598e180</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4035,19 +4035,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6885</v>
+        <v>9494</v>
       </c>
       <c r="G30" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="H30" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="I30" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
         <v>2</v>
@@ -4093,17 +4093,17 @@
         <v>1</v>
       </c>
       <c r="V30" t="n">
-        <v>33.11851951150082</v>
+        <v>2.34344395669909</v>
       </c>
       <c r="W30" t="n">
-        <v>0.03019458643532473</v>
+        <v>0.4267223874252885</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>332197cb5b6a5a986f6efa7872f2e14a541c05a54f2186232c3f3ef588fcd135</t>
+          <t>df8a0c217aea977b0555b4909474f4fa2f0dfa283b4f1a65c06ddf0196307603</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -4155,16 +4155,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5611</v>
+        <v>6877</v>
       </c>
       <c r="G31" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H31" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I31" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J31" t="n">
         <v>3</v>
@@ -4213,17 +4213,17 @@
         <v>1</v>
       </c>
       <c r="V31" t="n">
-        <v>2.604254681045377</v>
+        <v>1.658152502991723</v>
       </c>
       <c r="W31" t="n">
-        <v>0.3839870221903906</v>
+        <v>0.6030808373751808</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>41fe18c0a5cf584a20694655b9c436df30a233e7ce774424da1f3e28b1b8e0ff</t>
+          <t>96db0c05a31ae679fb9cc31d6375480d7871372310485112b460d1b78abd1bdd</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4275,19 +4275,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6490</v>
+        <v>3745</v>
       </c>
       <c r="G32" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="H32" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="I32" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
         <v>2</v>
@@ -4333,17 +4333,17 @@
         <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>2.621601574476699</v>
+        <v>10.91503976643994</v>
       </c>
       <c r="W32" t="n">
-        <v>0.3814462158307222</v>
+        <v>0.09161670698394173</v>
       </c>
       <c r="X32" t="b">
         <v>1</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>6e1a05cf97c71b4fca99f9c3620862bb9b42a72e8d61ee4f78b68ae709e66987</t>
+          <t>d8239f5a040230f2ec62f86d4f278f1a0b53bd3e6ee19247cb3ce81ca0cecfa9</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4395,22 +4395,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6711</v>
+        <v>5581</v>
       </c>
       <c r="G33" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="H33" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I33" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="J33" t="n">
         <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -4453,17 +4453,17 @@
         <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>12.7654552542889</v>
+        <v>60.08553334435669</v>
       </c>
       <c r="W33" t="n">
-        <v>0.07833641496365931</v>
+        <v>0.01664294122628307</v>
       </c>
       <c r="X33" t="b">
         <v>1</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>fa0845f774645fc9c1a805a182cdf4f9ca3ab7329a1cf85235e66b0af9b4286e</t>
+          <t>c9e0ddfec15ea306ff8a0ec9f0d9d317702e058c2975decc9ccb80056c0b91ac</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4515,16 +4515,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6042</v>
+        <v>9494</v>
       </c>
       <c r="G34" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="H34" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="I34" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="J34" t="n">
         <v>3</v>
@@ -4573,17 +4573,17 @@
         <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>2.711480254682066</v>
+        <v>2.34344395669909</v>
       </c>
       <c r="W34" t="n">
-        <v>0.3688022430822587</v>
+        <v>0.4267223874252885</v>
       </c>
       <c r="X34" t="b">
         <v>1</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>23c964e34760c24699e31b9f361b0bb11d59957eece49d362338d4d2e676fa5f</t>
+          <t>b42595202775a483e0df29700df80c3d0594123a83f82c9e4b3bc264a4d731db</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4635,16 +4635,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>7448</v>
+        <v>6877</v>
       </c>
       <c r="G35" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="H35" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I35" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="J35" t="n">
         <v>3</v>
@@ -4693,17 +4693,17 @@
         <v>1</v>
       </c>
       <c r="V35" t="n">
-        <v>43.65446438190501</v>
+        <v>1.658152502991723</v>
       </c>
       <c r="W35" t="n">
-        <v>0.02290716457431797</v>
+        <v>0.6030808373751808</v>
       </c>
       <c r="X35" t="b">
         <v>1</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>03eb635f35ddde004290db4bd328bed64b3158eef0f2508db62112fb771374e6</t>
+          <t>611cdc6f5c2c529f47111fa485beef424a19945a248c89ee6c2b1149793772d8</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -4755,22 +4755,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>7417</v>
+        <v>3745</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="H36" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="I36" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -4813,17 +4813,17 @@
         <v>1</v>
       </c>
       <c r="V36" t="n">
-        <v>14.01955766422533</v>
+        <v>10.91503976643994</v>
       </c>
       <c r="W36" t="n">
-        <v>0.07132892662881719</v>
+        <v>0.09161670698394173</v>
       </c>
       <c r="X36" t="b">
         <v>1</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>81db916378efdb156d3418aead1b5cbe4c2742c7623916b56fdefb745e763c6e</t>
+          <t>e97aa17dca31d425dd6cc128e4ae325662e30c5ef5f9d5668c68574c0be664dd</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4875,16 +4875,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4790</v>
+        <v>5581</v>
       </c>
       <c r="G37" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H37" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I37" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J37" t="n">
         <v>3</v>
@@ -4933,17 +4933,17 @@
         <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>8.942395573257013</v>
+        <v>60.08553334435669</v>
       </c>
       <c r="W37" t="n">
-        <v>0.1118268580055421</v>
+        <v>0.01664294122628307</v>
       </c>
       <c r="X37" t="b">
         <v>1</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>60ffc6dcf344ef8d95edbc596a560b977b6fd62fdb30c74889a6fb7856a1b4a7</t>
+          <t>800b8e419d82c4e372175cc47758af4f5630e6e08d962de42cc4877fca49ef4b</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4995,22 +4995,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>7504</v>
+        <v>9494</v>
       </c>
       <c r="G38" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="H38" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="I38" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="J38" t="n">
         <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5053,17 +5053,17 @@
         <v>1</v>
       </c>
       <c r="V38" t="n">
-        <v>14.83076775884473</v>
+        <v>2.34344395669909</v>
       </c>
       <c r="W38" t="n">
-        <v>0.06742739258415149</v>
+        <v>0.4267223874252885</v>
       </c>
       <c r="X38" t="b">
         <v>1</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>b5a0f593a88c07206dceef04066a965d0369cefb92b25778f02ac5e5e2915126</t>
+          <t>870358381bdf47ff43dd3a083a7aded2102a76889deceec7eda6325d956bab05</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5115,22 +5115,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>6457</v>
+        <v>6877</v>
       </c>
       <c r="G39" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="H39" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="I39" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -5173,17 +5173,17 @@
         <v>1</v>
       </c>
       <c r="V39" t="n">
-        <v>2.22503340746235</v>
+        <v>1.658152502991723</v>
       </c>
       <c r="W39" t="n">
-        <v>0.4494314542182536</v>
+        <v>0.6030808373751808</v>
       </c>
       <c r="X39" t="b">
         <v>1</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>78f016d67694cb37678e5344109448f0359995a2e93ddbfe7f20160783ee9106</t>
+          <t>077e24c4f3998c11242b903f7f738c61dd3c35d4cb63d03de6282e2d1e552fdc</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5235,16 +5235,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>7329</v>
+        <v>3745</v>
       </c>
       <c r="G40" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="H40" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="I40" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="J40" t="n">
         <v>2</v>
@@ -5293,17 +5293,17 @@
         <v>1</v>
       </c>
       <c r="V40" t="n">
-        <v>43.13884669019685</v>
+        <v>10.91503976643994</v>
       </c>
       <c r="W40" t="n">
-        <v>0.02318096279164659</v>
+        <v>0.09161670698394173</v>
       </c>
       <c r="X40" t="b">
         <v>1</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>e0315faf6d6b88aac755d3f1287f39a53e5dd6471ec2fd17a80ac39571e30071</t>
+          <t>8c86377f230bbc03cc633a880e2ddcca1f0d420cc1baf71aa79c10606f498090</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5355,19 +5355,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4407</v>
+        <v>5581</v>
       </c>
       <c r="G41" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H41" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I41" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
         <v>2</v>
@@ -5413,17 +5413,17 @@
         <v>1</v>
       </c>
       <c r="V41" t="n">
-        <v>13.58896358326708</v>
+        <v>60.08553334435669</v>
       </c>
       <c r="W41" t="n">
-        <v>0.07358912943378268</v>
+        <v>0.01664294122628307</v>
       </c>
       <c r="X41" t="b">
         <v>1</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2655f2d450102d2bdcda158f0ed1470cb2ab19640d559975e93090192669033e</t>
+          <t>3fa6a6c0a62c9258fdff0b7c9b537ebe9900615e9519a45c47e1679ece730121</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>10800</v>
+        <v>9494</v>
       </c>
       <c r="G42" t="n">
         <v>76</v>
@@ -5533,17 +5533,17 @@
         <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>8461540549.610653</v>
+        <v>4548632244.376826</v>
       </c>
       <c r="W42" t="n">
-        <v>1.181817890178419e-10</v>
+        <v>2.198463068181065e-10</v>
       </c>
       <c r="X42" t="b">
         <v>1</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>aa4aaf8529146125006219e4e4b0cd76665762ad9eb998fd2a00827e78ab6d10</t>
+          <t>4bc6542d1b858b7b02ffd2de9c9a39800521da76f371befe76bc2ffe9adca1f1</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5595,26 +5595,26 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3502</v>
+        <v>6877</v>
       </c>
       <c r="G43" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="H43" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="I43" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
         <v>2</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -5638,32 +5638,32 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>full_shrinkage</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>oas</t>
         </is>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0.0004298512162779192</v>
       </c>
       <c r="V43" t="n">
-        <v>547.2219318414583</v>
+        <v>586.3983258039873</v>
       </c>
       <c r="W43" t="n">
-        <v>0.001827412137219897</v>
+        <v>0.001705325469046873</v>
       </c>
       <c r="X43" t="b">
         <v>1</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>36b826e27ff6e5d3450d75b52ff97d7d508af675c4e6db80c11654f59b0a6c26</t>
+          <t>bd043a83fd2c9dbf5daefadf3cc3ddc1104fc324ee1cc86046fd6bd526c5cad2</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -5715,19 +5715,19 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6955</v>
+        <v>3745</v>
       </c>
       <c r="G44" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="H44" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="I44" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
         <v>2</v>
@@ -5767,23 +5767,23 @@
         </is>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
         <v>1</v>
       </c>
       <c r="V44" t="n">
-        <v>490.8364018067091</v>
+        <v>646.3054840670832</v>
       </c>
       <c r="W44" t="n">
-        <v>0.002037338706581503</v>
+        <v>0.001547255941118094</v>
       </c>
       <c r="X44" t="b">
         <v>1</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>4c0a0b620a11d1bb0718295f2abfc510e8dab0683e747270540d087f0111a37d</t>
+          <t>cfcbb9b966946cf0ebb84026f5a63067aa825fad21a06b3fee5181826eeecaea</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -5835,16 +5835,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>4440</v>
+        <v>5581</v>
       </c>
       <c r="G45" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H45" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I45" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J45" t="n">
         <v>3</v>
@@ -5893,17 +5893,17 @@
         <v>1</v>
       </c>
       <c r="V45" t="n">
-        <v>397464620.9744791</v>
+        <v>171822144.318474</v>
       </c>
       <c r="W45" t="n">
-        <v>2.515947199396671e-09</v>
+        <v>5.819971598925518e-09</v>
       </c>
       <c r="X45" t="b">
         <v>1</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>d9aa0963c5187fc4b0c0083cd9791f045d7b3e1b20faa9cb96fff7288f1200f0</t>
+          <t>2d878ae07974d7ddd24ad471032afbff948ff1c2d0e8adb7d823f76ec994c08a</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -5955,16 +5955,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>6654</v>
+        <v>9494</v>
       </c>
       <c r="G46" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="H46" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="I46" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="J46" t="n">
         <v>3</v>
@@ -6013,17 +6013,17 @@
         <v>1</v>
       </c>
       <c r="V46" t="n">
-        <v>11192328232.08947</v>
+        <v>4548632244.376826</v>
       </c>
       <c r="W46" t="n">
-        <v>8.934691507106668e-11</v>
+        <v>2.198463068181065e-10</v>
       </c>
       <c r="X46" t="b">
         <v>1</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>1a78a2f5fa2484071f164f399c2a6839137baa5ff9827df97487ce63a369a5b6</t>
+          <t>081bc6424789048c5419204f00ebefaa6208c5e6f414bd97d35967303b64f5a4</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -6075,26 +6075,26 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>6133</v>
+        <v>6877</v>
       </c>
       <c r="G47" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="H47" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="I47" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
         <v>2</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -6118,32 +6118,32 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>full_shrinkage</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>oas</t>
         </is>
       </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0.0004298512162779192</v>
       </c>
       <c r="V47" t="n">
-        <v>1802719625.868203</v>
+        <v>586.3983258039873</v>
       </c>
       <c r="W47" t="n">
-        <v>5.547174311803438e-10</v>
+        <v>0.001705325469046873</v>
       </c>
       <c r="X47" t="b">
         <v>1</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>8dd2a5ccd1b3b17c6621484fe430d59ef797ca702a860cb40ba9934b48075316</t>
+          <t>e77060b66d0da803fa7d452a88c2e0e5b1f334eab04e090adefde2ade337088a</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -6195,26 +6195,26 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>8707</v>
+        <v>3745</v>
       </c>
       <c r="G48" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="H48" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="I48" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
         <v>2</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -6238,32 +6238,32 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>full_shrinkage</t>
+          <t>diagonal_robust_z</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>oas</t>
+          <t>diagonal_robust_z</t>
         </is>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0.0002964966774197039</v>
+        <v>1</v>
       </c>
       <c r="V48" t="n">
-        <v>892.4921316107097</v>
+        <v>646.3054840670832</v>
       </c>
       <c r="W48" t="n">
-        <v>0.001120458057367117</v>
+        <v>0.001547255941118094</v>
       </c>
       <c r="X48" t="b">
         <v>1</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>e4da04dd3c99560022bb161e16358705e235d5170d826e8e8819cd6db2c746a1</t>
+          <t>f8edf396b6f2d1fde9340c5235c9d49c675232129ed1cf1584c5515f044fef22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6315,16 +6315,16 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4203</v>
+        <v>5581</v>
       </c>
       <c r="G49" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H49" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I49" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
@@ -6373,17 +6373,17 @@
         <v>1</v>
       </c>
       <c r="V49" t="n">
-        <v>726480717.4866781</v>
+        <v>171822144.318474</v>
       </c>
       <c r="W49" t="n">
-        <v>1.376499025961192e-09</v>
+        <v>5.819971598925518e-09</v>
       </c>
       <c r="X49" t="b">
         <v>1</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>9427a8db417a9c4eb595cfc56e6e2ded494d3fea5ad3e622fc365f6587dc47b6</t>
+          <t>aac17d433c6f51db20bdeda90d29506107ff5fe2e2456f9f66fb71d94c2df73d</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>9702</v>
+        <v>9494</v>
       </c>
       <c r="G50" t="n">
         <v>76</v>
@@ -6493,17 +6493,17 @@
         <v>1</v>
       </c>
       <c r="V50" t="n">
-        <v>12665745350.08422</v>
+        <v>4548632244.376826</v>
       </c>
       <c r="W50" t="n">
-        <v>7.895311111661904e-11</v>
+        <v>2.198463068181065e-10</v>
       </c>
       <c r="X50" t="b">
         <v>1</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>db7c9d684f24c90e83c16617e12f12c0bf152ca5961cccedd867c193559c79d4</t>
+          <t>b02883873ddd8c1ba2459a858d3fd6b2ae2df9f85aaa995ca65302a121478983</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -6555,26 +6555,26 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>5534</v>
+        <v>6877</v>
       </c>
       <c r="G51" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="H51" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="I51" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
         <v>2</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -6598,32 +6598,32 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>full_shrinkage</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>oas</t>
         </is>
       </c>
       <c r="T51" t="n">
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
+        <v>0.0004298512162779192</v>
       </c>
       <c r="V51" t="n">
-        <v>1926014567.249093</v>
+        <v>586.3983258039873</v>
       </c>
       <c r="W51" t="n">
-        <v>5.192068725774435e-10</v>
+        <v>0.001705325469046873</v>
       </c>
       <c r="X51" t="b">
         <v>1</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>7ef704f7d4d855e830325fc30b0068671964e0937e5033e330e5888557d11797</t>
+          <t>b4353e9414b8576c6879fe7aa9837a6f1ae7d34ba479cc257978670914ee0edf</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -6675,26 +6675,26 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>9299</v>
+        <v>3745</v>
       </c>
       <c r="G52" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="H52" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="I52" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
         <v>2</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -6718,32 +6718,32 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>full_shrinkage</t>
+          <t>diagonal_robust_z</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>oas</t>
+          <t>diagonal_robust_z</t>
         </is>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>0.0002810559937537716</v>
+        <v>1</v>
       </c>
       <c r="V52" t="n">
-        <v>790.4490888360596</v>
+        <v>646.3054840670832</v>
       </c>
       <c r="W52" t="n">
-        <v>0.001265103615303707</v>
+        <v>0.001547255941118094</v>
       </c>
       <c r="X52" t="b">
         <v>1</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>127727c7d0fee54a313b5bcff60b1f70ed797ab1a31a594235e3bb9c86518099</t>
+          <t>e786415cb5a4b671544fa40eefc2d7252a735a420bde231672491eccf9770dd5</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
@@ -6795,16 +6795,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1162</v>
+        <v>5581</v>
       </c>
       <c r="G53" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H53" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I53" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J53" t="n">
         <v>3</v>
@@ -6853,17 +6853,17 @@
         <v>1</v>
       </c>
       <c r="V53" t="n">
-        <v>5810015332.326042</v>
+        <v>171822144.318474</v>
       </c>
       <c r="W53" t="n">
-        <v>1.721165853790698e-10</v>
+        <v>5.819971598925518e-09</v>
       </c>
       <c r="X53" t="b">
         <v>1</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>273718e956cb688fbacce6e44a4907fdd83eed5e389935eee92f3304d9855ead</t>
+          <t>d32344028752583836e3b8e57b5fc127761258d11e379f8e189e6c407b020c46</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>10827</v>
+        <v>9494</v>
       </c>
       <c r="G54" t="n">
         <v>76</v>
@@ -6973,17 +6973,17 @@
         <v>1</v>
       </c>
       <c r="V54" t="n">
-        <v>8348815693.814693</v>
+        <v>4548632244.376826</v>
       </c>
       <c r="W54" t="n">
-        <v>1.1977746744857e-10</v>
+        <v>2.198463068181065e-10</v>
       </c>
       <c r="X54" t="b">
         <v>1</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>20f8e2aec909dee8293b5f2f089b880fd5cdac83668fb635e65a02f7fc6b57f2</t>
+          <t>f2ac0564122329d4f0705fe6f06d9f84ebc2244d7f660f49d1e8276225396ed8</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
@@ -7035,26 +7035,26 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>5246</v>
+        <v>6877</v>
       </c>
       <c r="G55" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="H55" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="I55" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="J55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -7078,32 +7078,32 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>full_shrinkage</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>diagonal_robust_z</t>
+          <t>oas</t>
         </is>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1</v>
+        <v>0.0004298512162779192</v>
       </c>
       <c r="V55" t="n">
-        <v>154.3255419632238</v>
+        <v>586.3983258039873</v>
       </c>
       <c r="W55" t="n">
-        <v>0.006479808768391059</v>
+        <v>0.001705325469046873</v>
       </c>
       <c r="X55" t="b">
         <v>1</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2ea3873346e379612724ea44d6618a767d9831c96ea9a7461831cd1efe3f8065</t>
+          <t>af8b26bf3b3847a8513a9bb4110230120cceb36ee344ab43d995964a73b3f1c8</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>5762</v>
+        <v>3745</v>
       </c>
       <c r="G56" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="H56" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="I56" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K56" t="n">
         <v>2</v>
@@ -7213,17 +7213,17 @@
         <v>1</v>
       </c>
       <c r="V56" t="n">
-        <v>363706617.1574178</v>
+        <v>646.3054840670832</v>
       </c>
       <c r="W56" t="n">
-        <v>2.749468810371368e-09</v>
+        <v>0.001547255941118094</v>
       </c>
       <c r="X56" t="b">
         <v>1</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>967ad611e7b7e2309bc298eb6c3ead5e9f42a4d1524b38cef87bb595f6cb3d74</t>
+          <t>f7f66637c8c890085cae4ad6a0d95058e58bc6f7099c28db3d9f0f97ee64d09e</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
@@ -7275,19 +7275,19 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3862</v>
+        <v>5581</v>
       </c>
       <c r="G57" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="H57" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="I57" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
         <v>2</v>
@@ -7333,17 +7333,17 @@
         <v>1</v>
       </c>
       <c r="V57" t="n">
-        <v>310.4233358136568</v>
+        <v>171822144.318474</v>
       </c>
       <c r="W57" t="n">
-        <v>0.003221407299740789</v>
+        <v>5.819971598925518e-09</v>
       </c>
       <c r="X57" t="b">
         <v>1</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>f7c73356a11a0a0a43190f1e9c71ac797b86ac8c039b134ae1df821b76ac9d32</t>
+          <t>e7833baa17184252541f3af028c2b0b7dfac7f887557d32a45e5197064bc6ee3</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_support_assessment.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_support_assessment.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="support" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'support'!$A$1:$AJ$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'support'!$A$1:$AL$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ57"/>
+  <dimension ref="A1:AL57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -464,8 +464,10 @@
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="19" customWidth="1" min="35" max="35"/>
-    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="29" customWidth="1" min="35" max="35"/>
+    <col width="30" customWidth="1" min="36" max="36"/>
+    <col width="19" customWidth="1" min="37" max="37"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -641,10 +643,20 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>research_topology_confirmed</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>production_topology_verified</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>topology_verified</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>open_topology_alerts</t>
         </is>
@@ -743,12 +755,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>abdea51b860497fc1b65b8107202a33c5eb4b613dfb71dc4bc9253e7c41cf23e</t>
+          <t>fb18033ca8cdf4f7c4ce5868487a5eb3a254953d1f99bf31afd1b627e6c22fca</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -766,9 +778,15 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -863,12 +881,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>9b64efc6f0dd32bc67a239eadf99ce765fd105a1787ad70df698a2d9c7634b96</t>
+          <t>99a601c6fa39787ce6068570a6b6a2ac383f5e60884715586d3ba9fb2628b8eb</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,9 +904,15 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -983,12 +1007,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>a4aaba002ac82a08dda34dba7ad4e4f9dc9719448181db8832de39d05ea5ee22</t>
+          <t>233e0282d4bc56c54a79999c161bba4e4555df12fd55d015407c4bc8f2cd700a</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,9 +1030,15 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1103,12 +1133,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>abd1e4cde2783685a74e7c221178b6478293e37ed48758c416f3cbc504c19296</t>
+          <t>7a7a4ccdab3382cedb22e8417cf9c580a6ccbf028d7b09e6411eb4bab9eb00ea</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,9 +1156,15 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1223,12 +1259,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>85bca70fde6b2e1d654d87d2ae97b54812b3bb28d37339d208a812bfd6f29c2d</t>
+          <t>39136504a94344514b5408a778a6c7117e04a9860ab6651949484ca4e5a1e050</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,9 +1282,15 @@
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1343,12 +1385,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4ef037901c0e763323e341ffb6e9f58d2450465d7f120798609ed300cc6e38cd</t>
+          <t>0d7a828cb28b3084b58b7beb4172531faf3f9060047c1d3c5f51f361cc936c08</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,9 +1408,15 @@
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1463,12 +1511,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>68781020732c583eee92cf61f32f95b45db7eeefafc5a0e63955bb1d1acaa43f</t>
+          <t>2c179a7a209d939fa83a9f1539be9b499c7b2acc62a1b4e92bb9a837878b14a0</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,9 +1534,15 @@
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1583,12 +1637,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5579197096f667e86500c1b654693513af672f096cd8755535d88ebf2751d9cf</t>
+          <t>4965d322313426ff447710cccea20e6ecbd65ebcd972cfb4b42ef81e8d7c47a4</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1606,9 +1660,15 @@
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1703,12 +1763,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1c31a0e46fc9ded7f2002a45fefb02020badecd80cdad6328c97f65f4488febe</t>
+          <t>354a6a72da76e35140d483ba5ab800a19e6d0ddaffde742d8359527196ab6a07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,9 +1786,15 @@
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1823,12 +1889,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0521c690ccc42e977d420c4fa4f20d1fb750179d6cf31452df4d7b85019e74a5</t>
+          <t>ada0e0882c629a46aa36e1af3e24574ec6c645fdbeacf5ec512573e6e5c6d1c1</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1846,9 +1912,15 @@
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1943,12 +2015,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>7f0a8af032795d53422a456427a61b6fc6b4e8c04a784ffa163e4a81c16f940d</t>
+          <t>1e5b165d4a1ac82af9c944c46392e3a2da20d131bf6b4d5e4253bbd42b572701</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1966,9 +2038,15 @@
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2063,12 +2141,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>192e2e3acc2cb7f14771418553f29f5470c80d7e76298c386ccf116cefa9b878</t>
+          <t>24ed9a2da8ce1b3e0cc94020d5191293e5db03f1673a2a125940a2414218dd90</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2086,9 +2164,15 @@
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2183,12 +2267,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>a1c7b40a3132bae1fe439735761785a3d781c4984759cdce66634cc2cedc86c6</t>
+          <t>64f83acef787ec08ccb0cbccc697f645037798eb344163f59a815809b4c4178b</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2206,9 +2290,15 @@
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2303,12 +2393,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>7b99b164f3ef6b07c79aeb92ad07985807e687e4fed0b5134a233f3d49a75475</t>
+          <t>aee70aa245242683ef06189f792d87a9cd9baa28e3bbdd771d7b401fb15faa69</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2326,9 +2416,15 @@
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2423,12 +2519,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1b2cb7dcdfb2637934e1963c48f936bb597aa6ffd1260145c9aaae5556c97d22</t>
+          <t>9488fdc873b3854237d5b986f7cef348786cb0f19037adbdaa20d52a4ed34438</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2446,9 +2542,15 @@
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2543,12 +2645,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>6e29ae2c103d43c43a5d3c04fdf0922c82db479d85bb75779e1162912a599314</t>
+          <t>bcc260c9a15ad9ddbbc522fc78377ccd0242c33b99a4c7a278867203919f80e3</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2566,9 +2668,15 @@
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2663,12 +2771,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>6011c4062b63c4fe6b193578d871299751d206923a96a85cd1da9298e753d52f</t>
+          <t>829d0231af279ec1db0ec81aee60669fab9a0aedd3c69f47260a9dcfa9181b1b</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2686,9 +2794,15 @@
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2783,12 +2897,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>124cfb18585941ef92e2001815553f7a971580a657f673d1a5582bc7a61eb0ac</t>
+          <t>9966ace0861eeeea114a8ca967654d05a05432c6dfb9db408de6f9614d143507</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2806,9 +2920,15 @@
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2903,12 +3023,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>163795178cb2ff51ce61ddc80b82e54e3402a0b2bb8e99fe2ade3f23df774ac2</t>
+          <t>4fa1ec62249883946aaae9be4747536b5857519f0beb13e00a6ad097b8195885</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2926,9 +3046,15 @@
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3023,12 +3149,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>e9690c753833b658d92c1d1fa7b906dc3597d30c2dfb2dfa650b94eb349ca09a</t>
+          <t>8157ecdddd343e461804600a940cdc2bebcf18128bef489db2ef696abc3e1407</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3046,9 +3172,15 @@
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3143,12 +3275,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>3e2ccd21062857aeb76fc468daf0e779f5b839da3fca7a760c444d714687b567</t>
+          <t>4237d5e306978d51585b94871e5b48389ecf672cb634b6b3be192f137a258149</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3166,9 +3298,15 @@
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3263,12 +3401,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>cc30ef322555343c07e03ebbae65fa1aff449c7cf32dc6429960014478228e00</t>
+          <t>321e27592b4d08ba633f919bae89262c00dd55b36a25e32a97f446cb5474d3e2</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3286,9 +3424,15 @@
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3383,12 +3527,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>1969ab355c6fb71ecae7af47809ec461e801d4aaf7c0cd9e1f4042d6fe01612c</t>
+          <t>f971e80d093526f764fc19b5f8c8eefae36151e6aa33782dae638350b6f4311f</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3406,9 +3550,15 @@
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3503,12 +3653,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>40d2dc4419104e2565f907677701af5d7520b3c1a66785887c2e8af250182fa9</t>
+          <t>00d6a8e94c9c1e232b297664f959a05169bb582fbddabea3e20abfc363bde052</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3526,9 +3676,15 @@
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3623,12 +3779,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>dd39d1c8e6ced0f9e58e8aa923803d356b6e61f3ca84af6e50d26e883ca3ec9b</t>
+          <t>56df21f55bf4411fcf8f27fa9658ad0685a438037ae26f0e77734c4074b25869</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3646,9 +3802,15 @@
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3743,12 +3905,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>13258aa831b746f55061aa4eb3753a9fce1281b5758506b8ddef633b6548a604</t>
+          <t>161d1b696a0865225712573fbae143ba66cb811c0143f2494b6cdcd9d4a43251</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3766,9 +3928,15 @@
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3863,12 +4031,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>ffd319fa76b84e7f36ef4ee99cb269065801e7fa2d07296cb1e91ec11da558f1</t>
+          <t>891817e5fc3e71aa5b47fb190cdb908134f1cf95071a21f23dc65c244dcf2e96</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3886,9 +4054,15 @@
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3983,12 +4157,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>d92b1d085d188c63ef369f7fa10d8e8c9dadf3aedd9cba2ec974b87be598e180</t>
+          <t>f18516ddacae40d3ad4e97a389dfdd42ce5be74376388b18e318a6aafdcab176</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4006,9 +4180,15 @@
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4103,12 +4283,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>df8a0c217aea977b0555b4909474f4fa2f0dfa283b4f1a65c06ddf0196307603</t>
+          <t>f13479c8dc2eec2b8b266550016a0e7a90fb216b71d5f32f9ead9ee7b0c8cdd1</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4126,9 +4306,15 @@
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4223,12 +4409,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>96db0c05a31ae679fb9cc31d6375480d7871372310485112b460d1b78abd1bdd</t>
+          <t>65839e77ed4d021683e4177a86cc182a1c4bf9b96601939f4c234386d339645c</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4246,9 +4432,15 @@
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4343,12 +4535,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>d8239f5a040230f2ec62f86d4f278f1a0b53bd3e6ee19247cb3ce81ca0cecfa9</t>
+          <t>9901b40e666825933ea61244eb9bd49709836d5d644345a48bc9efdf7d3fa939</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4366,9 +4558,15 @@
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4463,12 +4661,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>c9e0ddfec15ea306ff8a0ec9f0d9d317702e058c2975decc9ccb80056c0b91ac</t>
+          <t>6fef5d8d19e086068fc5c449a93b4834610b7b5e5fd5b0af00ad5943c6427410</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4486,9 +4684,15 @@
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4583,12 +4787,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>b42595202775a483e0df29700df80c3d0594123a83f82c9e4b3bc264a4d731db</t>
+          <t>cd79ce9cd9df7fbcefad18925f85e6507fce5f7ccd069c9688eb4d8822d3c95f</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4606,9 +4810,15 @@
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4703,12 +4913,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>611cdc6f5c2c529f47111fa485beef424a19945a248c89ee6c2b1149793772d8</t>
+          <t>d86bc56e94534e48668af3cb0ec805129294594ce114b6d96a7baba24167dd44</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4726,9 +4936,15 @@
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4823,12 +5039,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>e97aa17dca31d425dd6cc128e4ae325662e30c5ef5f9d5668c68574c0be664dd</t>
+          <t>d1bfae7c3733da72a8120e67e407593fa1250e052c21e542e66f1789cb8ed517</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4846,9 +5062,15 @@
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4943,12 +5165,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>800b8e419d82c4e372175cc47758af4f5630e6e08d962de42cc4877fca49ef4b</t>
+          <t>9e3a73a24e178c77c032945f49a0766baa2746676e66868212c4fbc96696c691</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4966,9 +5188,15 @@
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5063,12 +5291,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>870358381bdf47ff43dd3a083a7aded2102a76889deceec7eda6325d956bab05</t>
+          <t>247a585480e9c4a9bd426926a11915280e5d73c3055fb00611bc3dc5252908fb</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5086,9 +5314,15 @@
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5183,12 +5417,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>077e24c4f3998c11242b903f7f738c61dd3c35d4cb63d03de6282e2d1e552fdc</t>
+          <t>aaf398b0f00cef86e214954bca9ac8cf56464ee3c067da8e044891cb43ea0b1b</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5206,9 +5440,15 @@
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5303,12 +5543,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>8c86377f230bbc03cc633a880e2ddcca1f0d420cc1baf71aa79c10606f498090</t>
+          <t>5a1094b09f1132b73eae3d47472cdf4b27f20425dda238aef61fc8f272eb0136</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5326,9 +5566,15 @@
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5423,12 +5669,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>3fa6a6c0a62c9258fdff0b7c9b537ebe9900615e9519a45c47e1679ece730121</t>
+          <t>4bf6a5b5ae7d6ebda328336e6adc20e333ee780287b36c32f1d7822c4c64aadb</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5446,9 +5692,15 @@
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5543,12 +5795,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>4bc6542d1b858b7b02ffd2de9c9a39800521da76f371befe76bc2ffe9adca1f1</t>
+          <t>9ef217056ec569d206c11317f32d4c1f84c8f83ee2b82328a9e376547dfed732</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5566,9 +5818,15 @@
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5663,12 +5921,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>bd043a83fd2c9dbf5daefadf3cc3ddc1104fc324ee1cc86046fd6bd526c5cad2</t>
+          <t>89e67ee33ea2e745f4bad9f7229ae395893ae0d7eb8616b57bffa65fb3c88404</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5686,9 +5944,15 @@
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5783,12 +6047,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>cfcbb9b966946cf0ebb84026f5a63067aa825fad21a06b3fee5181826eeecaea</t>
+          <t>32ce5f36b60865c7630dfd31156777d72abb7b89cf5c939434a30858d355dd49</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5806,9 +6070,15 @@
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5903,12 +6173,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2d878ae07974d7ddd24ad471032afbff948ff1c2d0e8adb7d823f76ec994c08a</t>
+          <t>332f728f1af5a7ff9082613756745d42770ab601d96f853ea38aa3d8c58906f6</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5926,9 +6196,15 @@
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6023,12 +6299,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>081bc6424789048c5419204f00ebefaa6208c5e6f414bd97d35967303b64f5a4</t>
+          <t>a26f613e61dd2acb13fb8c0f5ebcb27b7e29aa1680b751fa7b739da8e9477ec9</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6046,9 +6322,15 @@
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6143,12 +6425,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>e77060b66d0da803fa7d452a88c2e0e5b1f334eab04e090adefde2ade337088a</t>
+          <t>fff62704786eef9f34876d78659741638c716b729fd4b5a02ff673fdc4784db7</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6166,9 +6448,15 @@
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6263,12 +6551,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>f8edf396b6f2d1fde9340c5235c9d49c675232129ed1cf1584c5515f044fef22</t>
+          <t>68f3cd49f5365c88dd17354375fcee551a149d2bf3c73527e30822401a1e006b</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6286,9 +6574,15 @@
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6383,12 +6677,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>aac17d433c6f51db20bdeda90d29506107ff5fe2e2456f9f66fb71d94c2df73d</t>
+          <t>14b4d256e1f636e4a32f333ff0fc6a59c30c4879648f3bb5fc9ecb68fe85160a</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6406,9 +6700,15 @@
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6503,12 +6803,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>b02883873ddd8c1ba2459a858d3fd6b2ae2df9f85aaa995ca65302a121478983</t>
+          <t>5842363d33687a7147f6ae2c2a5046eed28113cec18e1bd1db6bf429500b3f98</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6526,9 +6826,15 @@
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6623,12 +6929,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>b4353e9414b8576c6879fe7aa9837a6f1ae7d34ba479cc257978670914ee0edf</t>
+          <t>4e9f4af725dfc1d12a943b06dc4346b422a7d5f926c3e05305c439f264dd8397</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6646,9 +6952,15 @@
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6743,12 +7055,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>e786415cb5a4b671544fa40eefc2d7252a735a420bde231672491eccf9770dd5</t>
+          <t>45bc9fcd3bc1d8aef32fd7751c5d7093a575acefbb9289a250e6cb7c27e8dc39</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6766,9 +7078,15 @@
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6863,12 +7181,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>d32344028752583836e3b8e57b5fc127761258d11e379f8e189e6c407b020c46</t>
+          <t>2f0b301eb2ce02958724e2378da6f392be301e78219d6bd52ccc546ad7e2794e</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6886,9 +7204,15 @@
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6983,12 +7307,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>f2ac0564122329d4f0705fe6f06d9f84ebc2244d7f660f49d1e8276225396ed8</t>
+          <t>f8dcd87fa42461a4cc31fb29ce4fbd8acbe71534738fe7a34c88faa39230d083</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7006,9 +7330,15 @@
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7103,12 +7433,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>af8b26bf3b3847a8513a9bb4110230120cceb36ee344ab43d995964a73b3f1c8</t>
+          <t>c4aa8d985537012cd1e649aa42eb5810bdcf46c7bde03e3618b9b1386e1a184e</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7126,9 +7456,15 @@
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7223,12 +7559,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>f7f66637c8c890085cae4ad6a0d95058e58bc6f7099c28db3d9f0f97ee64d09e</t>
+          <t>9f26a19359e6bd6b599fc45c81254429b1350d64446b4a6727757d29e52d4239</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7246,9 +7582,15 @@
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7343,12 +7685,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>e7833baa17184252541f3af028c2b0b7dfac7f887557d32a45e5197064bc6ee3</t>
+          <t>626e40697aba5705ce619a5a16d74ab21a377bd55ffe7c43291a283d63e11a49</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>f2b0327f5fd5fbc10a96cbc361259c5e52098db43a174d469ed8c45852c78033</t>
+          <t>1e9138c373c38435b6d42c46a6f83777aa2501c0e67ad8f9094e59e3a884be39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7366,12 +7708,18 @@
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL57" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ57"/>
+  <autoFilter ref="A1:AL57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>